--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260929.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>10.00%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>8.80%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.20%</t>
+          <t>8.25%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>8.09%</t>
+          <t>8.06%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>7.06%</t>
         </is>
       </c>
     </row>
@@ -726,139 +726,139 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>6.08%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>24,757,000</t>
+          <t>7,389,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>4.78%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>7,320,000</t>
+          <t>24,757,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.78%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,499,000</t>
+          <t>87,118,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.71%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>87,118,000</t>
+          <t>2,499,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>4.57%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>6,264,000</t>
+          <t>8,937,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,937,000</t>
+          <t>6,264,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -875,78 +875,78 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>4,873,561</t>
+          <t>4,812,561</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.56%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>13,966,000</t>
+          <t>3,876,848</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,876,848</t>
+          <t>6,151,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,886,000</t>
+          <t>12,966,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,634,000</t>
+          <t>2,022,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,193,000</t>
+          <t>2,674,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1298,85 +1298,85 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>501,000</t>
+          <t>121,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>501,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>7,907,071,412</t>
+          <t>8,773,373,263</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2,141,350,397</t>
+          <t>2,094,635,197</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>8,934,608,591</t>
+          <t>7,063,520,391</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>3,482,132,473</t>
+          <t>3,005,175,390</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
